--- a/docs/Extras/SD2_S26/Reports-Documents/PCB-Assembly-Test-and-Operation/PCB Testing.xlsx
+++ b/docs/Extras/SD2_S26/Reports-Documents/PCB-Assembly-Test-and-Operation/PCB Testing.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="64">
   <si>
     <t>Step</t>
   </si>
@@ -88,6 +88,18 @@
     <t>No shorts</t>
   </si>
   <si>
+    <t>No shorts pre-assembly</t>
+  </si>
+  <si>
+    <t>- No shorts pre-assembly
+- Post-assembly, their might be 
+problems with 5V regulator</t>
+  </si>
+  <si>
+    <t>Did not assemble due to PCB design 
+not being funtional for intened purpose</t>
+  </si>
+  <si>
     <t>Power</t>
   </si>
   <si>
@@ -160,6 +172,51 @@
 </t>
   </si>
   <si>
+    <t>- 3.3V read 
+- J-Tag = 3.3V
+- PROG_ENn = 3.3V to 0.045V
+- Vref on JLINK is
+supposed to be 0V
+QPG6200 Internal pulls
+up nRESET pin (From
+datasheet pg 49)
+Dev kit is also getting
+3.3V at nRESET pin,
+TDO, TDI
+Tested board
+programming
+- No J-Tag connection
+- J-Tag_nRESET and
+TMS has 3.3V reading
+(For first test, not on
+second) (NOT
+SHORTED) on board 1
+- T-Tag nRESET is
+reading 3.3 (NOT TMS)
+(NO SHORT)
+Board 1 test 2:
+Error 1: Unable to read
+chip ID
+Error 2: pin override is
+not supported but
+required for the selected
+device
+Pins with ~3.3V: 3.3V
+pin, nRESET, TMS,
+TDO
+PROG_ENn switch cuts
+voltage from 3.3V to
+0.045V</t>
+  </si>
+  <si>
+    <t>- SW5 pulling 1.5A when powered on 
+- SW5 is to remain off when using device</t>
+  </si>
+  <si>
+    <t>Assembled to be shown as example and prop, 
+not to be shown for functionality</t>
+  </si>
+  <si>
     <t>IC Power</t>
   </si>
   <si>
@@ -196,6 +253,13 @@
     <t>Void (Needed new testing method)</t>
   </si>
   <si>
+    <t>Both power regulator are good</t>
+  </si>
+  <si>
+    <t>Error - unable to read power
+(problem wit 5V regulator)</t>
+  </si>
+  <si>
     <t>IC Overcurrent</t>
   </si>
   <si>
@@ -209,6 +273,16 @@
   </si>
   <si>
     <t>Void - board doesn’t support testing method</t>
+  </si>
+  <si>
+    <t>Did not conduct yet</t>
+  </si>
+  <si>
+    <t>Did not conduct due to IC and 
+regulator problems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7mA total = good </t>
   </si>
   <si>
     <t>Battery Test</t>
@@ -232,6 +306,14 @@
   </si>
   <si>
     <t>Could not perform due to footprints and J-Tag pin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battery power was good </t>
+  </si>
+  <si>
+    <t>- 7.3V 
+- Batteries are working with 
+device</t>
   </si>
   <si>
     <t>SMA Impedance</t>
@@ -272,6 +354,20 @@
     <t>SMA Impedance:
 - 2.4 GHz: 273 - 316j
 - 2.5 GHz: 12.3 - 47.3j</t>
+  </si>
+  <si>
+    <t>Not conducted yet</t>
+  </si>
+  <si>
+    <t>Currently testing - no 
+considerable changes 
+were observed</t>
+  </si>
+  <si>
+    <t>- Inconclusive data, numebrs 
+were not as expected due to 
+connections on NANO VNA and 
+SMA</t>
   </si>
 </sst>
 </file>
@@ -327,7 +423,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -360,9 +456,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -734,159 +827,255 @@
       <c r="G2" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="H2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>30</v>
+      <c r="L4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>35</v>
+        <v>43</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="12"/>
+        <v>51</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11"/>
+      <c r="T6" s="11"/>
+      <c r="U6" s="11"/>
+      <c r="V6" s="11"/>
+      <c r="W6" s="11"/>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="11"/>
+      <c r="Z6" s="11"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
-      <c r="V7" s="12"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="12"/>
-      <c r="Y7" s="12"/>
-      <c r="Z7" s="12"/>
+        <v>60</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="11"/>
+      <c r="V7" s="11"/>
+      <c r="W7" s="11"/>
+      <c r="X7" s="11"/>
+      <c r="Y7" s="11"/>
+      <c r="Z7" s="11"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
